--- a/data/garage_template_2.xlsx
+++ b/data/garage_template_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Drive E\EV Car\EV-Garage-Finder\EV-Garage-Finder\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B13DB61F-4C61-4BF5-B51B-BE1FD7534DB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8036AB06-E284-4D2B-BA76-3A7258CD959A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1301,7 +1301,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1313,6 +1313,12 @@
       <u/>
       <sz val="12"/>
       <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1689,8 +1695,9 @@
     <col min="2" max="3" width="14.8125" customWidth="1"/>
     <col min="4" max="4" width="22.8125" customWidth="1"/>
     <col min="5" max="5" width="20.8125" customWidth="1"/>
-    <col min="6" max="6" width="34.8125" customWidth="1"/>
-    <col min="7" max="8" width="14.8125" customWidth="1"/>
+    <col min="6" max="6" width="38.625" customWidth="1"/>
+    <col min="7" max="7" width="16.8125" customWidth="1"/>
+    <col min="8" max="8" width="14.8125" customWidth="1"/>
     <col min="9" max="9" width="16.8125" customWidth="1"/>
     <col min="10" max="10" width="26.8125" customWidth="1"/>
     <col min="11" max="11" width="43.6875" customWidth="1"/>
@@ -3438,6 +3445,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="K3" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="L8" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
